--- a/public/inputs/y02-science - input.xlsx
+++ b/public/inputs/y02-science - input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unit 1 · Environments and habitats</t>
+          <t>Unit 1 · Living things in their environment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.1 Habitats</t>
+          <t>1.1 Asking questions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -467,7 +467,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.2 Plants in different habitats</t>
+          <t>1.2 What is an environment?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -480,7 +480,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.3 Animals in different habitats</t>
+          <t>1.3 Compare natural environments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -493,7 +493,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.4 Rocks and the environment</t>
+          <t>1.4 Plants in different habitats</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.5 How can we care for our environment?</t>
+          <t>1.5 Animals in different habitats</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -514,12 +514,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unit 2 · Forces and movement</t>
+          <t>1.6 Exploring local environments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.1 Forces around us</t>
+          <t>1.7 Investigate a local environment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -540,12 +540,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.2 Changing shape</t>
+          <t>Unit 2 · Humans and other animals</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.3 Changing speed</t>
+          <t>2.1 Humans and other animals</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.4 Changing direction</t>
+          <t>2.2 Animals and their offsprings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -579,12 +579,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unit 3 · Getting materials right</t>
+          <t>2.3 Do we look like our parents?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -597,7 +597,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3.1 Natural and made materials</t>
+          <t>2.4 Keeping healthy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3.2 Properties of materials</t>
+          <t>2.5 Diet and exercise are important</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -623,7 +623,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3.3 Using the right material</t>
+          <t>2.6 Signs of illness</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3.4 Testing materials</t>
+          <t>2.7 Human teeth</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3.5 Changing materials</t>
+          <t>2.8 Dentists and science</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unit 4 · Humans and animals grow</t>
+          <t>Unit 3 · Matter and Materials</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -675,7 +675,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.1 Comparing animals</t>
+          <t>3.1 Measuring</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.2 Growing</t>
+          <t>3.2 Natural materials</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4.3 Inheriting characteristics</t>
+          <t>3.3 Manufactured materials</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.4 Keeping healthy</t>
+          <t>3.4 Properties of materials</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.5 Teeth</t>
+          <t>3.5 Hard or soft?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -735,12 +735,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Unit 5 · Light</t>
+          <t>3.6 Strength</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5.1 Light sources</t>
+          <t>3.7 Flexibility</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5.2 Darkness</t>
+          <t>3.8 Uses of materials</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -779,7 +779,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5.3 The sun appears to move!</t>
+          <t>3.9 Changing materials</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -787,12 +787,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Subunit</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Unit 6 · Electricity</t>
+          <t>3.10 Sports Equipment</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -800,12 +800,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Subunit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6.1 Where do we use electricity?</t>
+          <t>Unit 4 · Forces</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -818,7 +818,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6.2 Keep safe with electricity</t>
+          <t>4.1 Modelling</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -831,10 +831,465 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6.3 Making circuits</t>
+          <t>4.2 Forces and movement</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4.3 Changing the shape of an object</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4.4 Speeding up and slowing down</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4.5 Changing direction</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unit 5 · Light and electricity</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5.1 Sources of light</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5.2 Light and dark</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5.3 Lighting in our homes</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5.4 Where is the sun?</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5.5 Using electricity</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5.6 What is a circuit?</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5.7 Building circuits</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unit 6 · The Earth's crust</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>6.1 Using sources</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>6.2 Different types of rocks</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>6.3 Rocks are useful</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>6.4 Mining the Earth</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Subunit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>6.5 Mining in Madagascar</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Term 1 Revision</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Term 1 Assessment</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Term 1 Animal Theory</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Term 1 Animal and Plant Practicals</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Term 1 Plant Theory</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Term 1 School Activities</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Term 2 Revision</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Term 2 Assessment</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Term 2 Animal Theory</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Term 2 Animal and Plant Practicals</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Term 2 Plant Theory</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Term 2 School Activities</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Term 3 Revision</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Term 3 Assessment</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Term 3 Animal Theory</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Term 3 Animal and Plant Practicals</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Term 3 Plant Theory</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Term 3 School Activities</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
